--- a/测试集/泛用性验收_v3/W1/W1_反馈_市场营销部.xlsx
+++ b/测试集/泛用性验收_v3/W1/W1_反馈_市场营销部.xlsx
@@ -17,13 +17,17 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="14"/>
     </font>
     <font>
       <name val="微软雅黑"/>
@@ -70,15 +74,25 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
+  <dxfs count="1">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00C6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -440,115 +454,161 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>任务编号</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>任务名称</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>责任单位</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>月份</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>计划数量</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>预算金额(元)</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>状态</t>
+          <t>2026年度重点工作任务计划表</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>T005</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>完成资料汇总</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>市场营销部</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>5月</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>50</v>
-      </c>
-      <c r="F2">
-        <f>E2*100</f>
-        <v/>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>已完成</t>
+          <t>说明：金额单位为元，数量为计划数。</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>编制单位：综合办公室    日期：2026-01-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>任务编号</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>任务名称</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>责任单位</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>月份</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>计划数量</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>预算金额(元)</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>状态</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>T005</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>完成资料汇总</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>市场营销部</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>5月</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>50</v>
+      </c>
+      <c r="F5">
+        <f>E5*100</f>
+        <v/>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>T010</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>应急预案修订</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>市场营销部</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>10月</t>
         </is>
       </c>
-      <c r="E3" t="n">
+      <c r="E6" t="n">
         <v>100</v>
       </c>
-      <c r="F3">
-        <f>E3*100</f>
+      <c r="F6">
+        <f>E6*100</f>
         <v/>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>已完成</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A1:G1"/>
+  </mergeCells>
+  <conditionalFormatting sqref="G5:G6">
+    <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
+      <formula>"已完成"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="G5:G6" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"进行中,已完成,已取消"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape"/>
 </worksheet>
 </file>